--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ARKANSAS_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ARKANSAS_2010.xlsx
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C109">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C133">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C421">
@@ -12984,7 +12984,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C702">
